--- a/data/trans_dic/DC_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,37; 28,19</t>
+          <t>21,52; 28,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,26; 41,67</t>
+          <t>29,91; 41,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,14; 34,04</t>
+          <t>28,39; 34,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 21,78</t>
+          <t>7,75; 21,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,67; 43,1</t>
+          <t>37,66; 42,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,16; 31,2</t>
+          <t>17,99; 31,31</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,26; 27,34</t>
+          <t>20,48; 27,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,11; 74,87</t>
+          <t>39,06; 76,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,51; 61,03</t>
+          <t>31,21; 59,42</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 27,34</t>
+          <t>21,48; 26,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,34; 54,98</t>
+          <t>38,12; 53,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,45; 43,63</t>
+          <t>31,34; 42,06</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 23,88</t>
+          <t>16,48; 23,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,58; 54,24</t>
+          <t>39,55; 54,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,83; 40,09</t>
+          <t>30,08; 39,43</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>135781; 179152</t>
+          <t>136739; 178896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>204943; 302228</t>
+          <t>216940; 303478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>369349; 463139</t>
+          <t>386359; 466159</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>112513; 259818</t>
+          <t>92443; 257655</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>361120; 413141</t>
+          <t>361002; 410771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>390670; 671170</t>
+          <t>387146; 673678</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142779; 192632</t>
+          <t>144353; 193976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>365001; 698819</t>
+          <t>364538; 711000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>516068; 999725</t>
+          <t>511311; 973407</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>197486; 253420</t>
+          <t>199088; 249727</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>419769; 602001</t>
+          <t>417398; 588530</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>635878; 882065</t>
+          <t>633539; 850434</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>593275; 826212</t>
+          <t>570239; 823821</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1469461; 2013722</t>
+          <t>1468343; 2005111</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2139444; 2875621</t>
+          <t>2157419; 2827859</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 28,15</t>
+          <t>20,91; 27,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,91; 41,84</t>
+          <t>37,64; 43,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,39; 34,26</t>
+          <t>30,36; 34,93</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 21,6</t>
+          <t>18,18; 23,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,66; 42,85</t>
+          <t>37,67; 43,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,99; 31,31</t>
+          <t>28,77; 32,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,48; 27,53</t>
+          <t>20,82; 27,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,06; 76,18</t>
+          <t>39,5; 45,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,21; 59,42</t>
+          <t>31,09; 35,73</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 26,94</t>
+          <t>20,97; 26,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,12; 53,75</t>
+          <t>36,56; 41,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,34; 42,06</t>
+          <t>30,08; 33,92</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,48; 23,81</t>
+          <t>21,51; 24,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39,55; 54,01</t>
+          <t>39,19; 41,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,08; 39,43</t>
+          <t>30,88; 33,05</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>157098</t>
+          <t>167791</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>297130</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431137</t>
+          <t>464921</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>136739; 178896</t>
+          <t>144424; 189164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>216940; 303478</t>
+          <t>276357; 320840</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>386359; 466159</t>
+          <t>432553; 497741</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>197650</t>
+          <t>216435</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>386459</t>
+          <t>433846</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584109</t>
+          <t>650281</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92443; 257655</t>
+          <t>190721; 248138</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>361002; 410771</t>
+          <t>403579; 462161</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>387146; 673678</t>
+          <t>609951; 690270</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>167575</t>
+          <t>191823</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>500704</t>
+          <t>345442</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668279</t>
+          <t>537264</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>144353; 193976</t>
+          <t>167187; 217940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>364538; 711000</t>
+          <t>320822; 371543</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>511311; 973407</t>
+          <t>502271; 577185</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>225274</t>
+          <t>233185</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>472548</t>
+          <t>438945</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>697822</t>
+          <t>672131</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>199088; 249727</t>
+          <t>207589; 261470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>417398; 588530</t>
+          <t>409140; 466899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>633539; 850434</t>
+          <t>634346; 715443</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>747597</t>
+          <t>809235</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1633750</t>
+          <t>1515362</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2381347</t>
+          <t>2324597</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>570239; 823821</t>
+          <t>759866; 864592</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1468343; 2005111</t>
+          <t>1464653; 1567010</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2157419; 2827859</t>
+          <t>2244812; 2402482</t>
         </is>
       </c>
     </row>
